--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2488,7 +2488,7 @@
         <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -3421,10 +3421,10 @@
         <v>46</v>
       </c>
       <c r="F124" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G124" t="n">
-        <v>78.0</v>
+        <v>77.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -590,7 +590,7 @@
         <v>0.0</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="H15" t="n">
         <v>0.0</v>
@@ -3476,10 +3476,10 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>476.0</v>
+        <v>477.0</v>
       </c>
       <c r="H126" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1292,7 +1292,7 @@
         <v>1.0</v>
       </c>
       <c r="G42" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>172.0</v>
       </c>
       <c r="H69" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="70">

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3476,7 +3476,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>477.0</v>
+        <v>476.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3788,7 +3788,7 @@
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="49">
   <si>
     <t>Area</t>
   </si>
@@ -1422,7 +1422,7 @@
         <v>1.0</v>
       </c>
       <c r="G47" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1474,7 +1474,7 @@
         <v>0.0</v>
       </c>
       <c r="G49" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1945,7 +1945,7 @@
         <v>37.0</v>
       </c>
       <c r="H67" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="68">
@@ -2072,7 +2072,7 @@
         <v>0.0</v>
       </c>
       <c r="G72" t="n">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2384,7 +2384,7 @@
         <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2592,10 +2592,10 @@
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>36.0</v>
+        <v>35.0</v>
       </c>
       <c r="H92" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="93">
@@ -2618,7 +2618,7 @@
         <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="H93" t="n">
         <v>2.0</v>
@@ -3424,7 +3424,7 @@
         <v>11.0</v>
       </c>
       <c r="G124" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3447,10 +3447,10 @@
         <v>42</v>
       </c>
       <c r="F125" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G125" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3476,7 +3476,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>476.0</v>
+        <v>481.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C136" t="s">
         <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>37</v>
-      </c>
-      <c r="E136" t="e">
-        <v>#N/A</v>
+        <v>36</v>
+      </c>
+      <c r="E136" t="s">
+        <v>48</v>
       </c>
       <c r="F136" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G136" t="n">
         <v>0.0</v>
@@ -3747,22 +3747,22 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G137" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3773,22 +3773,22 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>37</v>
-      </c>
-      <c r="E138" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="E138" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G138" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3799,22 +3799,22 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="G139" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3825,22 +3825,22 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>37</v>
-      </c>
-      <c r="E140" t="e">
-        <v>#N/A</v>
+        <v>36</v>
+      </c>
+      <c r="E140" t="s">
+        <v>43</v>
       </c>
       <c r="F140" t="n">
-        <v>1.0</v>
+        <v>23.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3851,22 +3851,22 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E141" t="s">
         <v>42</v>
       </c>
       <c r="F141" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G141" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3877,22 +3877,22 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F142" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3903,25 +3903,25 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E143" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G143" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="144">
@@ -3929,7 +3929,7 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3937,14 +3937,14 @@
       <c r="D144" t="s">
         <v>37</v>
       </c>
-      <c r="E144" t="s">
-        <v>43</v>
+      <c r="E144" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3955,7 +3955,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3964,13 +3964,13 @@
         <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F145" t="n">
         <v>0.0</v>
       </c>
       <c r="G145" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3981,7 +3981,7 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -3990,13 +3990,13 @@
         <v>37</v>
       </c>
       <c r="E146" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F146" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4007,19 +4007,19 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F147" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
         <v>3.0</v>
@@ -4039,16 +4039,16 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>38</v>
-      </c>
-      <c r="E148" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="E148" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F148" t="n">
         <v>1.0</v>
       </c>
       <c r="G148" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4065,16 +4065,16 @@
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4091,16 +4091,16 @@
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G150" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4111,19 +4111,19 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E151" t="s">
         <v>46</v>
       </c>
       <c r="F151" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G151" t="n">
         <v>1.0</v>
@@ -4137,22 +4137,22 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E152" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F152" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4163,22 +4163,22 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F153" t="n">
         <v>0.0</v>
       </c>
       <c r="G153" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4195,16 +4195,16 @@
         <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E154" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G154" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4215,22 +4215,22 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F155" t="n">
         <v>1.0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4241,22 +4241,22 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
       </c>
       <c r="D156" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F156" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4267,22 +4267,22 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C157" t="s">
         <v>17</v>
       </c>
       <c r="D157" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F157" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G157" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4293,22 +4293,22 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C158" t="s">
         <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F158" t="n">
         <v>0.0</v>
       </c>
       <c r="G158" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4319,22 +4319,22 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C159" t="s">
         <v>17</v>
       </c>
       <c r="D159" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G159" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4345,16 +4345,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4371,22 +4371,22 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F161" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4397,22 +4397,22 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E162" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F162" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G162" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4429,16 +4429,16 @@
         <v>17</v>
       </c>
       <c r="D163" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F163" t="n">
         <v>1.0</v>
       </c>
       <c r="G163" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4455,16 +4455,16 @@
         <v>17</v>
       </c>
       <c r="D164" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F164" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4475,22 +4475,22 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
       </c>
       <c r="D165" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F165" t="n">
         <v>1.0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4501,16 +4501,16 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
       </c>
       <c r="D166" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F166" t="n">
         <v>0.0</v>
@@ -4533,13 +4533,13 @@
         <v>17</v>
       </c>
       <c r="D167" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F167" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G167" t="n">
         <v>2.0</v>
@@ -4553,22 +4553,22 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C168" t="s">
         <v>17</v>
       </c>
       <c r="D168" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F168" t="n">
         <v>1.0</v>
       </c>
       <c r="G168" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4579,22 +4579,22 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C169" t="s">
         <v>17</v>
       </c>
       <c r="D169" t="s">
-        <v>41</v>
-      </c>
-      <c r="E169" t="s">
-        <v>42</v>
+        <v>39</v>
+      </c>
+      <c r="E169" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G169" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4605,22 +4605,22 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
       </c>
       <c r="D170" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G170" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4631,22 +4631,22 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
       </c>
       <c r="D171" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E171" t="s">
         <v>43</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="G171" t="n">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
       <c r="H171" t="n">
         <v>0.0</v>
@@ -4657,22 +4657,22 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
       </c>
       <c r="D172" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E172" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F172" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H172" t="n">
         <v>0.0</v>
@@ -4683,22 +4683,22 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C173" t="s">
         <v>17</v>
       </c>
       <c r="D173" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E173" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F173" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H173" t="n">
         <v>0.0</v>
@@ -4709,22 +4709,22 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C174" t="s">
         <v>17</v>
       </c>
       <c r="D174" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E174" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F174" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="G174" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H174" t="n">
         <v>0.0</v>
@@ -4735,22 +4735,22 @@
         <v>8</v>
       </c>
       <c r="B175" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C175" t="s">
         <v>17</v>
       </c>
       <c r="D175" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E175" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F175" t="n">
         <v>1.0</v>
       </c>
       <c r="G175" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H175" t="n">
         <v>0.0</v>
@@ -4761,19 +4761,19 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
       </c>
       <c r="D176" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F176" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -4787,24 +4787,414 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>40</v>
+      </c>
+      <c r="E177" t="s">
+        <v>43</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178" t="s">
+        <v>9</v>
+      </c>
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" t="s">
+        <v>40</v>
+      </c>
+      <c r="E178" t="s">
+        <v>44</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" t="s">
+        <v>9</v>
+      </c>
+      <c r="C179" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179" t="s">
+        <v>40</v>
+      </c>
+      <c r="E179" t="s">
+        <v>45</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" t="s">
+        <v>40</v>
+      </c>
+      <c r="E180" t="s">
+        <v>46</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" t="s">
+        <v>40</v>
+      </c>
+      <c r="E181" t="s">
+        <v>42</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" t="s">
+        <v>41</v>
+      </c>
+      <c r="E182" t="s">
+        <v>48</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>8</v>
+      </c>
+      <c r="B183" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" t="s">
+        <v>41</v>
+      </c>
+      <c r="E183" t="s">
+        <v>43</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G183" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>8</v>
+      </c>
+      <c r="B184" t="s">
+        <v>9</v>
+      </c>
+      <c r="C184" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184" t="s">
+        <v>41</v>
+      </c>
+      <c r="E184" t="s">
+        <v>42</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185" t="s">
+        <v>9</v>
+      </c>
+      <c r="C185" t="s">
+        <v>17</v>
+      </c>
+      <c r="D185" t="s">
+        <v>41</v>
+      </c>
+      <c r="E185" t="s">
+        <v>44</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186" t="s">
+        <v>12</v>
+      </c>
+      <c r="C186" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" t="s">
+        <v>41</v>
+      </c>
+      <c r="E186" t="s">
+        <v>43</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187" t="s">
         <v>10</v>
       </c>
-      <c r="C177" t="s">
-        <v>17</v>
-      </c>
-      <c r="D177" t="s">
+      <c r="C187" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" t="s">
         <v>41</v>
       </c>
-      <c r="E177" t="s">
+      <c r="E187" t="s">
+        <v>48</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" t="s">
+        <v>10</v>
+      </c>
+      <c r="C188" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" t="s">
+        <v>41</v>
+      </c>
+      <c r="E188" t="s">
+        <v>47</v>
+      </c>
+      <c r="F188" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" t="s">
+        <v>41</v>
+      </c>
+      <c r="E189" t="s">
+        <v>46</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" t="s">
+        <v>41</v>
+      </c>
+      <c r="E190" t="s">
+        <v>43</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>41</v>
+      </c>
+      <c r="E191" t="s">
+        <v>44</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>8</v>
+      </c>
+      <c r="B192" t="s">
+        <v>10</v>
+      </c>
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" t="s">
+        <v>41</v>
+      </c>
+      <c r="E192" t="s">
         <v>45</v>
       </c>
-      <c r="F177" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G177" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H177" t="n">
+      <c r="F192" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H192" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1994,7 +1994,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>172.0</v>
+        <v>171.0</v>
       </c>
       <c r="H69" t="n">
         <v>33.0</v>
@@ -3450,7 +3450,7 @@
         <v>11.0</v>
       </c>
       <c r="G125" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3606,7 +3606,7 @@
         <v>2.0</v>
       </c>
       <c r="G131" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1292,7 +1292,7 @@
         <v>1.0</v>
       </c>
       <c r="G42" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1318,7 +1318,7 @@
         <v>0.0</v>
       </c>
       <c r="G43" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3476,7 +3476,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>481.0</v>
+        <v>482.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3424,7 +3424,7 @@
         <v>11.0</v>
       </c>
       <c r="G124" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3476,7 +3476,7 @@
         <v>3.0</v>
       </c>
       <c r="G126" t="n">
-        <v>482.0</v>
+        <v>480.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="49">
   <si>
     <t>Area</t>
   </si>
@@ -2020,7 +2020,7 @@
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2693,10 +2693,10 @@
         <v>42</v>
       </c>
       <c r="F96" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G96" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2774,7 +2774,7 @@
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2785,7 +2785,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2794,13 +2794,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F100" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G100" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2811,7 +2811,7 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C101" t="s">
         <v>16</v>
@@ -2820,13 +2820,13 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
         <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2846,13 +2846,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2863,25 +2863,25 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E103" t="s">
         <v>42</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G103" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="104">
@@ -2889,22 +2889,22 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C104" t="s">
         <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2924,16 +2924,16 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G105" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -2941,7 +2941,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2967,7 +2967,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -2976,7 +2976,7 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
@@ -2985,7 +2985,7 @@
         <v>2.0</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="108">
@@ -2993,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -3001,14 +3001,14 @@
       <c r="D108" t="s">
         <v>32</v>
       </c>
-      <c r="E108" t="s">
-        <v>42</v>
+      <c r="E108" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G108" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3019,7 +3019,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3031,10 +3031,10 @@
         <v>46</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G109" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3045,7 +3045,7 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
@@ -3057,13 +3057,13 @@
         <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G110" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="H110" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -3079,14 +3079,14 @@
       <c r="D111" t="s">
         <v>32</v>
       </c>
-      <c r="E111" t="e">
-        <v>#N/A</v>
+      <c r="E111" t="s">
+        <v>44</v>
       </c>
       <c r="F111" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3097,13 +3097,13 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C112" t="s">
         <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E112" t="s">
         <v>46</v>
@@ -3112,7 +3112,7 @@
         <v>3.0</v>
       </c>
       <c r="G112" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3123,22 +3123,22 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C113" t="s">
         <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E113" t="s">
         <v>42</v>
       </c>
       <c r="F113" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G113" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3149,22 +3149,22 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E114" t="s">
         <v>44</v>
       </c>
       <c r="F114" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G114" t="n">
-        <v>17.0</v>
+        <v>36.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3184,13 +3184,13 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F115" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G115" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3201,7 +3201,7 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C116" t="s">
         <v>16</v>
@@ -3210,13 +3210,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F116" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G116" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3227,7 +3227,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3236,13 +3236,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F117" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G117" t="n">
         <v>3.0</v>
-      </c>
-      <c r="G117" t="n">
-        <v>36.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3253,7 +3253,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C118" t="s">
         <v>16</v>
@@ -3262,13 +3262,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3288,13 +3288,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3305,7 +3305,7 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
@@ -3313,17 +3313,17 @@
       <c r="D120" t="s">
         <v>33</v>
       </c>
-      <c r="E120" t="s">
-        <v>46</v>
+      <c r="E120" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F120" t="n">
         <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="121">
@@ -3331,7 +3331,7 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C121" t="s">
         <v>16</v>
@@ -3340,13 +3340,13 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>79.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3357,7 +3357,7 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C122" t="s">
         <v>16</v>
@@ -3366,13 +3366,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G122" t="n">
-        <v>3.0</v>
+        <v>24.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3391,17 +3391,17 @@
       <c r="D123" t="s">
         <v>33</v>
       </c>
-      <c r="E123" t="e">
-        <v>#N/A</v>
+      <c r="E123" t="s">
+        <v>44</v>
       </c>
       <c r="F123" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0</v>
+        <v>480.0</v>
       </c>
       <c r="H123" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -3418,13 +3418,13 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F124" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G124" t="n">
-        <v>79.0</v>
+        <v>0.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3441,16 +3441,16 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>33</v>
-      </c>
-      <c r="E125" t="s">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="E125" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F125" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="G125" t="n">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3467,16 +3467,16 @@
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E126" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F126" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G126" t="n">
-        <v>480.0</v>
+        <v>0.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3493,16 +3493,16 @@
         <v>16</v>
       </c>
       <c r="D127" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E127" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F127" t="n">
         <v>2.0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3521,14 +3521,14 @@
       <c r="D128" t="s">
         <v>34</v>
       </c>
-      <c r="E128" t="e">
-        <v>#N/A</v>
+      <c r="E128" t="s">
+        <v>44</v>
       </c>
       <c r="F128" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G128" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3545,16 +3545,16 @@
         <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E129" t="s">
         <v>46</v>
       </c>
       <c r="F129" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3571,19 +3571,19 @@
         <v>16</v>
       </c>
       <c r="D130" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E130" t="s">
         <v>42</v>
       </c>
       <c r="F130" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G130" t="n">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="131">
@@ -3597,13 +3597,13 @@
         <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E131" t="s">
         <v>44</v>
       </c>
       <c r="F131" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G131" t="n">
         <v>10.0</v>
@@ -3617,22 +3617,22 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C132" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D132" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G132" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3646,22 +3646,22 @@
         <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G133" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="H133" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="134">
@@ -3672,19 +3672,19 @@
         <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G134" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3695,7 +3695,7 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C135" t="s">
         <v>17</v>
@@ -3703,14 +3703,14 @@
       <c r="D135" t="s">
         <v>36</v>
       </c>
-      <c r="E135" t="s">
-        <v>43</v>
+      <c r="E135" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F135" t="n">
         <v>1.0</v>
       </c>
       <c r="G135" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3730,13 +3730,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F136" t="n">
-        <v>5.0</v>
+        <v>35.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3756,13 +3756,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F137" t="n">
-        <v>3.0</v>
+        <v>23.0</v>
       </c>
       <c r="G137" t="n">
-        <v>2.0</v>
+        <v>26.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3781,11 +3781,11 @@
       <c r="D138" t="s">
         <v>36</v>
       </c>
-      <c r="E138" t="e">
-        <v>#N/A</v>
+      <c r="E138" t="s">
+        <v>42</v>
       </c>
       <c r="F138" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -3808,13 +3808,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F139" t="n">
-        <v>35.0</v>
+        <v>9.0</v>
       </c>
       <c r="G139" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3834,16 +3834,16 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F140" t="n">
-        <v>23.0</v>
+        <v>8.0</v>
       </c>
       <c r="G140" t="n">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="141">
@@ -3851,19 +3851,19 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
-      </c>
-      <c r="E141" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="E141" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F141" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
@@ -3877,22 +3877,22 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F142" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3903,25 +3903,25 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H143" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="144">
@@ -3937,14 +3937,14 @@
       <c r="D144" t="s">
         <v>37</v>
       </c>
-      <c r="E144" t="e">
-        <v>#N/A</v>
+      <c r="E144" t="s">
+        <v>44</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3955,7 +3955,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3963,14 +3963,14 @@
       <c r="D145" t="s">
         <v>37</v>
       </c>
-      <c r="E145" t="s">
-        <v>43</v>
+      <c r="E145" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G145" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3981,7 +3981,7 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -3993,10 +3993,10 @@
         <v>42</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G146" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4007,7 +4007,7 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -4016,13 +4016,13 @@
         <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G147" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4041,14 +4041,14 @@
       <c r="D148" t="s">
         <v>37</v>
       </c>
-      <c r="E148" t="e">
-        <v>#N/A</v>
+      <c r="E148" t="s">
+        <v>46</v>
       </c>
       <c r="F148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4068,13 +4068,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F149" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4094,13 +4094,13 @@
         <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F150" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4111,7 +4111,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4123,10 +4123,10 @@
         <v>46</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G151" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4143,16 +4143,16 @@
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E152" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4169,16 +4169,16 @@
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4189,22 +4189,22 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C154" t="s">
         <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F154" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4224,13 +4224,13 @@
         <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F155" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G155" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4241,7 +4241,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -4250,13 +4250,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F156" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G156" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4267,7 +4267,7 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C157" t="s">
         <v>17</v>
@@ -4276,13 +4276,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G157" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4293,7 +4293,7 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C158" t="s">
         <v>17</v>
@@ -4302,13 +4302,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F158" t="n">
         <v>0.0</v>
       </c>
       <c r="G158" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4328,13 +4328,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F159" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G159" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G159" t="n">
-        <v>1.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4345,16 +4345,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E160" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F160" t="n">
         <v>1.0</v>
@@ -4371,22 +4371,22 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G161" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4397,22 +4397,22 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G162" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4432,13 +4432,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F163" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4458,13 +4458,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F164" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G164" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4475,7 +4475,7 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
@@ -4484,13 +4484,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F165" t="n">
         <v>1.0</v>
       </c>
       <c r="G165" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4501,7 +4501,7 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -4509,11 +4509,11 @@
       <c r="D166" t="s">
         <v>39</v>
       </c>
-      <c r="E166" t="s">
-        <v>48</v>
+      <c r="E166" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G166" t="n">
         <v>1.0</v>
@@ -4527,7 +4527,7 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C167" t="s">
         <v>17</v>
@@ -4536,10 +4536,10 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G167" t="n">
         <v>2.0</v>
@@ -4562,13 +4562,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F168" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4587,14 +4587,14 @@
       <c r="D169" t="s">
         <v>39</v>
       </c>
-      <c r="E169" t="e">
-        <v>#N/A</v>
+      <c r="E169" t="s">
+        <v>42</v>
       </c>
       <c r="F169" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G169" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4614,13 +4614,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F170" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="G170" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4640,13 +4640,13 @@
         <v>39</v>
       </c>
       <c r="E171" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F171" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="G171" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="H171" t="n">
         <v>0.0</v>
@@ -4657,22 +4657,22 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
       </c>
       <c r="D172" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E172" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F172" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G172" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H172" t="n">
         <v>0.0</v>
@@ -4683,22 +4683,22 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C173" t="s">
         <v>17</v>
       </c>
       <c r="D173" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E173" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F173" t="n">
         <v>3.0</v>
       </c>
       <c r="G173" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H173" t="n">
         <v>0.0</v>
@@ -4709,22 +4709,22 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C174" t="s">
         <v>17</v>
       </c>
       <c r="D174" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E174" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F174" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H174" t="n">
         <v>0.0</v>
@@ -4744,13 +4744,13 @@
         <v>40</v>
       </c>
       <c r="E175" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F175" t="n">
         <v>1.0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H175" t="n">
         <v>0.0</v>
@@ -4770,10 +4770,10 @@
         <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F176" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -4787,7 +4787,7 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C177" t="s">
         <v>17</v>
@@ -4796,13 +4796,13 @@
         <v>40</v>
       </c>
       <c r="E177" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F177" t="n">
         <v>1.0</v>
       </c>
       <c r="G177" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -4813,7 +4813,7 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C178" t="s">
         <v>17</v>
@@ -4822,10 +4822,10 @@
         <v>40</v>
       </c>
       <c r="E178" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F178" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G178" t="n">
         <v>1.0</v>
@@ -4845,16 +4845,16 @@
         <v>17</v>
       </c>
       <c r="D179" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E179" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F179" t="n">
         <v>1.0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -4865,22 +4865,22 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C180" t="s">
         <v>17</v>
       </c>
       <c r="D180" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E180" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F180" t="n">
         <v>1.0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H180" t="n">
         <v>0.0</v>
@@ -4891,13 +4891,13 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C181" t="s">
         <v>17</v>
       </c>
       <c r="D181" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E181" t="s">
         <v>42</v>
@@ -4906,7 +4906,7 @@
         <v>0.0</v>
       </c>
       <c r="G181" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H181" t="n">
         <v>0.0</v>
@@ -4926,13 +4926,13 @@
         <v>41</v>
       </c>
       <c r="E182" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F182" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G182" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H182" t="n">
         <v>0.0</v>
@@ -4943,7 +4943,7 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -4955,10 +4955,10 @@
         <v>43</v>
       </c>
       <c r="F183" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G183" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H183" t="n">
         <v>0.0</v>
@@ -4969,7 +4969,7 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
@@ -4978,13 +4978,13 @@
         <v>41</v>
       </c>
       <c r="E184" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G184" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H184" t="n">
         <v>0.0</v>
@@ -4995,7 +4995,7 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C185" t="s">
         <v>17</v>
@@ -5004,13 +5004,13 @@
         <v>41</v>
       </c>
       <c r="E185" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F185" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H185" t="n">
         <v>0.0</v>
@@ -5021,7 +5021,7 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C186" t="s">
         <v>17</v>
@@ -5030,10 +5030,10 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F186" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G186" t="n">
         <v>1.0</v>
@@ -5056,13 +5056,13 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F187" t="n">
         <v>1.0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H187" t="n">
         <v>0.0</v>
@@ -5082,7 +5082,7 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F188" t="n">
         <v>2.0</v>
@@ -5108,93 +5108,15 @@
         <v>41</v>
       </c>
       <c r="E189" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F189" t="n">
         <v>1.0</v>
       </c>
       <c r="G189" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H189" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>8</v>
-      </c>
-      <c r="B190" t="s">
-        <v>10</v>
-      </c>
-      <c r="C190" t="s">
-        <v>17</v>
-      </c>
-      <c r="D190" t="s">
-        <v>41</v>
-      </c>
-      <c r="E190" t="s">
-        <v>43</v>
-      </c>
-      <c r="F190" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G190" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="H190" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>8</v>
-      </c>
-      <c r="B191" t="s">
-        <v>10</v>
-      </c>
-      <c r="C191" t="s">
-        <v>17</v>
-      </c>
-      <c r="D191" t="s">
-        <v>41</v>
-      </c>
-      <c r="E191" t="s">
-        <v>44</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H191" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>8</v>
-      </c>
-      <c r="B192" t="s">
-        <v>10</v>
-      </c>
-      <c r="C192" t="s">
-        <v>17</v>
-      </c>
-      <c r="D192" t="s">
-        <v>41</v>
-      </c>
-      <c r="E192" t="s">
-        <v>45</v>
-      </c>
-      <c r="F192" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H192" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3398,7 +3398,7 @@
         <v>3.0</v>
       </c>
       <c r="G123" t="n">
-        <v>480.0</v>
+        <v>479.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -4386,7 +4386,7 @@
         <v>3.0</v>
       </c>
       <c r="G161" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -590,7 +590,7 @@
         <v>0.0</v>
       </c>
       <c r="G15" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="H15" t="n">
         <v>0.0</v>
@@ -4539,7 +4539,7 @@
         <v>46</v>
       </c>
       <c r="F167" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G167" t="n">
         <v>2.0</v>
@@ -4565,7 +4565,7 @@
         <v>43</v>
       </c>
       <c r="F168" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G168" t="n">
         <v>29.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1971,7 +1971,7 @@
         <v>16.0</v>
       </c>
       <c r="H68" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="69">

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1292,7 +1292,7 @@
         <v>1.0</v>
       </c>
       <c r="G42" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -4100,7 +4100,7 @@
         <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3343,7 +3343,7 @@
         <v>46</v>
       </c>
       <c r="F121" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G121" t="n">
         <v>79.0</v>
@@ -3398,7 +3398,7 @@
         <v>3.0</v>
       </c>
       <c r="G123" t="n">
-        <v>479.0</v>
+        <v>478.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -434,7 +434,7 @@
         <v>1.0</v>
       </c>
       <c r="G9" t="n">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="49">
   <si>
     <t>Area</t>
   </si>
@@ -850,7 +850,7 @@
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="H25" t="n">
         <v>0.0</v>
@@ -1994,7 +1994,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>171.0</v>
+        <v>170.0</v>
       </c>
       <c r="H69" t="n">
         <v>33.0</v>
@@ -4354,10 +4354,10 @@
         <v>39</v>
       </c>
       <c r="E160" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F160" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -4380,13 +4380,13 @@
         <v>39</v>
       </c>
       <c r="E161" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F161" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4406,13 +4406,13 @@
         <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F162" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G162" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4432,13 +4432,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F163" t="n">
         <v>0.0</v>
       </c>
       <c r="G163" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4449,7 +4449,7 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -4458,13 +4458,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G164" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4483,14 +4483,14 @@
       <c r="D165" t="s">
         <v>39</v>
       </c>
-      <c r="E165" t="s">
-        <v>48</v>
+      <c r="E165" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F165" t="n">
         <v>1.0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4509,14 +4509,14 @@
       <c r="D166" t="s">
         <v>39</v>
       </c>
-      <c r="E166" t="e">
-        <v>#N/A</v>
+      <c r="E166" t="s">
+        <v>46</v>
       </c>
       <c r="F166" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G166" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4536,13 +4536,13 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F167" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="G167" t="n">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4562,13 +4562,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F168" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G168" t="n">
-        <v>29.0</v>
+        <v>5.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4588,13 +4588,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F169" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G169" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4614,13 +4614,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F170" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
       <c r="G170" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4631,19 +4631,19 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
       </c>
       <c r="D171" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E171" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F171" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
@@ -4666,10 +4666,10 @@
         <v>40</v>
       </c>
       <c r="E172" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F172" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G172" t="n">
         <v>0.0</v>
@@ -4692,13 +4692,13 @@
         <v>40</v>
       </c>
       <c r="E173" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F173" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H173" t="n">
         <v>0.0</v>
@@ -4718,13 +4718,13 @@
         <v>40</v>
       </c>
       <c r="E174" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F174" t="n">
         <v>1.0</v>
       </c>
       <c r="G174" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H174" t="n">
         <v>0.0</v>
@@ -4744,13 +4744,13 @@
         <v>40</v>
       </c>
       <c r="E175" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F175" t="n">
         <v>1.0</v>
       </c>
       <c r="G175" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H175" t="n">
         <v>0.0</v>
@@ -4761,7 +4761,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
@@ -4770,7 +4770,7 @@
         <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F176" t="n">
         <v>1.0</v>
@@ -4796,13 +4796,13 @@
         <v>40</v>
       </c>
       <c r="E177" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F177" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -4813,22 +4813,22 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C178" t="s">
         <v>17</v>
       </c>
       <c r="D178" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E178" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G178" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H178" t="n">
         <v>0.0</v>
@@ -4848,13 +4848,13 @@
         <v>41</v>
       </c>
       <c r="E179" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F179" t="n">
         <v>1.0</v>
       </c>
       <c r="G179" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -4874,13 +4874,13 @@
         <v>41</v>
       </c>
       <c r="E180" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F180" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G180" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H180" t="n">
         <v>0.0</v>
@@ -4900,13 +4900,13 @@
         <v>41</v>
       </c>
       <c r="E181" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F181" t="n">
         <v>0.0</v>
       </c>
       <c r="G181" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="H181" t="n">
         <v>0.0</v>
@@ -4917,7 +4917,7 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C182" t="s">
         <v>17</v>
@@ -4926,13 +4926,13 @@
         <v>41</v>
       </c>
       <c r="E182" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F182" t="n">
         <v>0.0</v>
       </c>
       <c r="G182" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="H182" t="n">
         <v>0.0</v>
@@ -4943,7 +4943,7 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -4952,13 +4952,13 @@
         <v>41</v>
       </c>
       <c r="E183" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G183" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H183" t="n">
         <v>0.0</v>
@@ -4978,10 +4978,10 @@
         <v>41</v>
       </c>
       <c r="E184" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F184" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G184" t="n">
         <v>0.0</v>
@@ -5004,13 +5004,13 @@
         <v>41</v>
       </c>
       <c r="E185" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F185" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H185" t="n">
         <v>0.0</v>
@@ -5030,13 +5030,13 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F186" t="n">
         <v>1.0</v>
       </c>
       <c r="G186" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H186" t="n">
         <v>0.0</v>
@@ -5056,13 +5056,13 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F187" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G187" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H187" t="n">
         <v>0.0</v>
@@ -5082,41 +5082,15 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F188" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G188" t="n">
         <v>0.0</v>
       </c>
       <c r="H188" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>8</v>
-      </c>
-      <c r="B189" t="s">
-        <v>10</v>
-      </c>
-      <c r="C189" t="s">
-        <v>17</v>
-      </c>
-      <c r="D189" t="s">
-        <v>41</v>
-      </c>
-      <c r="E189" t="s">
-        <v>45</v>
-      </c>
-      <c r="F189" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H189" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -2176,7 +2176,7 @@
         <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -3398,7 +3398,7 @@
         <v>3.0</v>
       </c>
       <c r="G123" t="n">
-        <v>478.0</v>
+        <v>477.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -798,7 +798,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>70.0</v>
+        <v>69.0</v>
       </c>
       <c r="H23" t="n">
         <v>0.0</v>
@@ -2176,7 +2176,7 @@
         <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1812,7 +1812,7 @@
         <v>0.0</v>
       </c>
       <c r="G62" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -3398,7 +3398,7 @@
         <v>3.0</v>
       </c>
       <c r="G123" t="n">
-        <v>477.0</v>
+        <v>476.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1240,7 +1240,7 @@
         <v>0.0</v>
       </c>
       <c r="G40" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -4516,7 +4516,7 @@
         <v>10.0</v>
       </c>
       <c r="G166" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3629,7 +3629,7 @@
         <v>43</v>
       </c>
       <c r="F132" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G132" t="n">
         <v>4.0</v>
@@ -4542,7 +4542,7 @@
         <v>13.0</v>
       </c>
       <c r="G167" t="n">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -4617,7 +4617,7 @@
         <v>45</v>
       </c>
       <c r="F170" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1994,7 +1994,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="H69" t="n">
         <v>33.0</v>
@@ -2124,7 +2124,7 @@
         <v>1.0</v>
       </c>
       <c r="G74" t="n">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -3372,7 +3372,7 @@
         <v>11.0</v>
       </c>
       <c r="G122" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3528,7 +3528,7 @@
         <v>2.0</v>
       </c>
       <c r="G128" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3993,7 +3993,7 @@
         <v>42</v>
       </c>
       <c r="F146" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G146" t="n">
         <v>15.0</v>
@@ -4074,7 +4074,7 @@
         <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4854,7 +4854,7 @@
         <v>1.0</v>
       </c>
       <c r="G179" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -5030,13 +5030,13 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F186" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G186" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H186" t="n">
         <v>0.0</v>
@@ -5056,10 +5056,10 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F187" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -5082,13 +5082,13 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F188" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H188" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1994,7 +1994,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>171.0</v>
+        <v>170.0</v>
       </c>
       <c r="H69" t="n">
         <v>33.0</v>
@@ -2176,7 +2176,7 @@
         <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2852,7 +2852,7 @@
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -3086,7 +3086,7 @@
         <v>2.0</v>
       </c>
       <c r="G111" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3372,7 +3372,7 @@
         <v>11.0</v>
       </c>
       <c r="G122" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3398,7 +3398,7 @@
         <v>3.0</v>
       </c>
       <c r="G123" t="n">
-        <v>476.0</v>
+        <v>475.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -4594,7 +4594,7 @@
         <v>3.0</v>
       </c>
       <c r="G169" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -1916,7 +1916,7 @@
         <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1994,10 +1994,10 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="H69" t="n">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="70">
@@ -4386,7 +4386,7 @@
         <v>1.0</v>
       </c>
       <c r="G161" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -4152,7 +4152,7 @@
         <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -3242,7 +3242,7 @@
         <v>1.0</v>
       </c>
       <c r="G117" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3294,7 +3294,7 @@
         <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="49">
   <si>
     <t>Area</t>
   </si>
@@ -844,13 +844,13 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="H25" t="n">
         <v>0.0</v>
@@ -861,7 +861,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -870,13 +870,13 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -922,13 +922,13 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -947,8 +947,8 @@
       <c r="D29" t="s">
         <v>20</v>
       </c>
-      <c r="E29" t="e">
-        <v>#N/A</v>
+      <c r="E29" t="s">
+        <v>47</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -973,14 +973,14 @@
       <c r="D30" t="s">
         <v>20</v>
       </c>
-      <c r="E30" t="s">
-        <v>44</v>
+      <c r="E30" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>26.0</v>
+        <v>1.0</v>
       </c>
       <c r="H30" t="n">
         <v>0.0</v>
@@ -991,22 +991,22 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
       </c>
       <c r="G31" t="n">
-        <v>1.0</v>
+        <v>26.0</v>
       </c>
       <c r="H31" t="n">
         <v>0.0</v>
@@ -1017,22 +1017,22 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
       </c>
       <c r="G32" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H32" t="n">
         <v>0.0</v>
@@ -1052,13 +1052,13 @@
         <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>
       </c>
       <c r="G33" t="n">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="H33" t="n">
         <v>0.0</v>
@@ -1069,7 +1069,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -1078,13 +1078,13 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1095,7 +1095,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -1104,13 +1104,13 @@
         <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1130,13 +1130,13 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G36" t="n">
-        <v>27.0</v>
+        <v>3.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1156,13 +1156,13 @@
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G37" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1173,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
@@ -1182,13 +1182,13 @@
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F38" t="n">
         <v>0.0</v>
       </c>
       <c r="G38" t="n">
-        <v>3.0</v>
+        <v>27.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1199,7 +1199,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
@@ -1208,13 +1208,13 @@
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
       </c>
       <c r="G39" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
       <c r="H39" t="n">
         <v>0.0</v>
@@ -1234,13 +1234,13 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
       </c>
       <c r="G40" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -1251,19 +1251,19 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F41" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -1277,22 +1277,22 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
         <v>44</v>
       </c>
       <c r="F42" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G42" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G43" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1329,7 +1329,7 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -1338,13 +1338,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F44" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G44" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1355,7 +1355,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -1370,7 +1370,7 @@
         <v>0.0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1390,13 +1390,13 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G46" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1407,7 +1407,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -1416,13 +1416,13 @@
         <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1433,7 +1433,7 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
@@ -1442,13 +1442,13 @@
         <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1468,13 +1468,13 @@
         <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G49" t="n">
-        <v>114.0</v>
+        <v>13.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1485,22 +1485,22 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1511,22 +1511,22 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E51" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F51" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G51" t="n">
-        <v>22.0</v>
+        <v>119.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1546,13 +1546,13 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F52" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1572,13 +1572,13 @@
         <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G53" t="n">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="H53" t="n">
         <v>0.0</v>
@@ -1595,10 +1595,10 @@
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E54" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F54" t="n">
         <v>1.0</v>
@@ -1621,16 +1621,16 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F55" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G55" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1650,7 +1650,7 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
         <v>1.0</v>
@@ -1676,13 +1676,13 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F57" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1702,13 +1702,13 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G58" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1719,22 +1719,22 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G59" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1745,22 +1745,22 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F60" t="n">
         <v>0.0</v>
       </c>
       <c r="G60" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H60" t="n">
         <v>0.0</v>
@@ -1771,7 +1771,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -1780,13 +1780,13 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F61" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G61" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1797,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -1806,13 +1806,13 @@
         <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F62" t="n">
         <v>0.0</v>
       </c>
       <c r="G62" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1832,13 +1832,13 @@
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G63" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H63" t="n">
         <v>0.0</v>
@@ -1849,7 +1849,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1875,7 +1875,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -1884,13 +1884,13 @@
         <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F65" t="n">
         <v>0.0</v>
       </c>
       <c r="G65" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1910,13 +1910,13 @@
         <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G66" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1930,22 +1930,22 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>37.0</v>
+        <v>2.0</v>
       </c>
       <c r="H67" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1956,22 +1956,22 @@
         <v>11</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F68" t="n">
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="H68" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
@@ -1988,16 +1988,16 @@
         <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>171.0</v>
+        <v>37.0</v>
       </c>
       <c r="H69" t="n">
-        <v>32.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="70">
@@ -2011,19 +2011,19 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F70" t="n">
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>33.0</v>
+        <v>16.0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="71">
@@ -2037,19 +2037,19 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E71" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F71" t="n">
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>3.0</v>
+        <v>171.0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="72">
@@ -2066,13 +2066,13 @@
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
       </c>
       <c r="G72" t="n">
-        <v>68.0</v>
+        <v>33.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" t="e">
-        <v>#N/A</v>
+        <v>27</v>
+      </c>
+      <c r="E73" t="s">
+        <v>42</v>
       </c>
       <c r="F73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2115,16 +2115,16 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F74" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G74" t="n">
-        <v>17.0</v>
+        <v>68.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2143,14 +2143,14 @@
       <c r="D75" t="s">
         <v>28</v>
       </c>
-      <c r="E75" t="s">
-        <v>42</v>
+      <c r="E75" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F75" t="n">
         <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2170,13 +2170,13 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F76" t="n">
         <v>1.0</v>
       </c>
       <c r="G76" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2196,16 +2196,16 @@
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G77" t="n">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="H77" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -2213,22 +2213,22 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F78" t="n">
         <v>1.0</v>
       </c>
       <c r="G78" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2239,25 +2239,25 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>29</v>
-      </c>
-      <c r="E79" t="e">
-        <v>#N/A</v>
+        <v>28</v>
+      </c>
+      <c r="E79" t="s">
+        <v>43</v>
       </c>
       <c r="F79" t="n">
         <v>0.0</v>
       </c>
       <c r="G79" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="80">
@@ -2274,13 +2274,13 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2291,7 +2291,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2300,13 +2300,13 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G81" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2326,13 +2326,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F82" t="n">
         <v>1.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2352,13 +2352,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F83" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2378,13 +2378,13 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F84" t="n">
         <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2395,7 +2395,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
         <v>15</v>
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G85" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2429,14 +2429,14 @@
       <c r="D86" t="s">
         <v>29</v>
       </c>
-      <c r="E86" t="s">
-        <v>42</v>
+      <c r="E86" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F86" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2462,7 +2462,7 @@
         <v>0.0</v>
       </c>
       <c r="G87" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H87" t="n">
         <v>0.0</v>
@@ -2488,7 +2488,7 @@
         <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>13.0</v>
+        <v>21.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2696,7 +2696,7 @@
         <v>4.0</v>
       </c>
       <c r="G96" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2826,7 +2826,7 @@
         <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -4828,7 +4828,7 @@
         <v>1.0</v>
       </c>
       <c r="G178" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H178" t="n">
         <v>0.0</v>
@@ -4854,7 +4854,7 @@
         <v>1.0</v>
       </c>
       <c r="G179" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -4906,7 +4906,7 @@
         <v>0.0</v>
       </c>
       <c r="G181" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="H181" t="n">
         <v>0.0</v>
@@ -4926,7 +4926,7 @@
         <v>41</v>
       </c>
       <c r="E182" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F182" t="n">
         <v>0.0</v>
@@ -4943,7 +4943,7 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -4952,13 +4952,13 @@
         <v>41</v>
       </c>
       <c r="E183" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F183" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H183" t="n">
         <v>0.0</v>
@@ -4969,7 +4969,7 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
@@ -4978,13 +4978,13 @@
         <v>41</v>
       </c>
       <c r="E184" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F184" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H184" t="n">
         <v>0.0</v>
@@ -5004,13 +5004,13 @@
         <v>41</v>
       </c>
       <c r="E185" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F185" t="n">
         <v>1.0</v>
       </c>
       <c r="G185" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H185" t="n">
         <v>0.0</v>
@@ -5030,7 +5030,7 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F186" t="n">
         <v>2.0</v>
@@ -5056,13 +5056,13 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F187" t="n">
         <v>1.0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H187" t="n">
         <v>0.0</v>
@@ -5082,15 +5082,67 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
+        <v>44</v>
+      </c>
+      <c r="F188" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" t="s">
+        <v>41</v>
+      </c>
+      <c r="E189" t="s">
+        <v>45</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" t="s">
+        <v>41</v>
+      </c>
+      <c r="E190" t="s">
         <v>43</v>
       </c>
-      <c r="F188" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G188" t="n">
+      <c r="F190" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G190" t="n">
         <v>4.0</v>
       </c>
-      <c r="H188" t="n">
+      <c r="H190" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/farms_ZR.xlsx
+++ b/Download/farms_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="49">
   <si>
     <t>Area</t>
   </si>
@@ -2248,16 +2248,16 @@
         <v>28</v>
       </c>
       <c r="E79" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F79" t="n">
         <v>0.0</v>
       </c>
       <c r="G79" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -2265,25 +2265,25 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
         <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="81">
@@ -2291,7 +2291,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2300,13 +2300,13 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F81" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2326,13 +2326,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F82" t="n">
         <v>1.0</v>
       </c>
       <c r="G82" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2352,13 +2352,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G83" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2378,13 +2378,13 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F84" t="n">
         <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2395,7 +2395,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
         <v>15</v>
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F85" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G85" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>15.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2429,14 +2429,14 @@
       <c r="D86" t="s">
         <v>29</v>
       </c>
-      <c r="E86" t="e">
-        <v>#N/A</v>
+      <c r="E86" t="s">
+        <v>42</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G86" t="n">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2455,14 +2455,14 @@
       <c r="D87" t="s">
         <v>29</v>
       </c>
-      <c r="E87" t="s">
-        <v>46</v>
+      <c r="E87" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F87" t="n">
         <v>0.0</v>
       </c>
       <c r="G87" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="H87" t="n">
         <v>0.0</v>
@@ -2482,13 +2482,13 @@
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F88" t="n">
         <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>21.0</v>
+        <v>10.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2505,16 +2505,16 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F89" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -2534,16 +2534,16 @@
         <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F90" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G90" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H90" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="91">
@@ -2560,16 +2560,16 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G91" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="H91" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="92">
@@ -2586,16 +2586,16 @@
         <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F92" t="n">
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>35.0</v>
+        <v>5.0</v>
       </c>
       <c r="H92" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="93">
@@ -2612,13 +2612,13 @@
         <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F93" t="n">
         <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>15.0</v>
+        <v>35.0</v>
       </c>
       <c r="H93" t="n">
         <v>2.0</v>
@@ -2629,13 +2629,13 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E94" t="s">
         <v>42</v>
@@ -2644,10 +2644,10 @@
         <v>0.0</v>
       </c>
       <c r="G94" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="95">
@@ -2664,13 +2664,13 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F95" t="n">
         <v>0.0</v>
       </c>
       <c r="G95" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2681,7 +2681,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2690,13 +2690,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F96" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G96" t="n">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2715,14 +2715,14 @@
       <c r="D97" t="s">
         <v>31</v>
       </c>
-      <c r="E97" t="e">
-        <v>#N/A</v>
+      <c r="E97" t="s">
+        <v>42</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G97" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2741,8 +2741,8 @@
       <c r="D98" t="s">
         <v>31</v>
       </c>
-      <c r="E98" t="s">
-        <v>46</v>
+      <c r="E98" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F98" t="n">
         <v>0.0</v>
@@ -2768,13 +2768,13 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F99" t="n">
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2785,7 +2785,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2794,13 +2794,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F100" t="n">
         <v>0.0</v>
       </c>
       <c r="G100" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2820,13 +2820,13 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F101" t="n">
         <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2846,13 +2846,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2863,25 +2863,25 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G103" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -2898,16 +2898,16 @@
         <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G104" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="105">
@@ -2924,13 +2924,13 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F105" t="n">
         <v>0.0</v>
       </c>
       <c r="G105" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H105" t="n">
         <v>0.0</v>
@@ -2941,7 +2941,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2950,13 +2950,13 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F106" t="n">
         <v>0.0</v>
       </c>
       <c r="G106" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2976,16 +2976,16 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H107" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="108">
@@ -2993,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -3001,17 +3001,17 @@
       <c r="D108" t="s">
         <v>32</v>
       </c>
-      <c r="E108" t="e">
-        <v>#N/A</v>
+      <c r="E108" t="s">
+        <v>42</v>
       </c>
       <c r="F108" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="109">
@@ -3027,14 +3027,14 @@
       <c r="D109" t="s">
         <v>32</v>
       </c>
-      <c r="E109" t="s">
-        <v>46</v>
+      <c r="E109" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F109" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G109" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3054,13 +3054,13 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F110" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G110" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3080,13 +3080,13 @@
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F111" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G111" t="n">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3097,22 +3097,22 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C112" t="s">
         <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F112" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G112" t="n">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3132,13 +3132,13 @@
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F113" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G113" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3158,13 +3158,13 @@
         <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F114" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G114" t="n">
-        <v>36.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3184,13 +3184,13 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F115" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3201,7 +3201,7 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C116" t="s">
         <v>16</v>
@@ -3210,10 +3210,10 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F116" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -3236,13 +3236,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F117" t="n">
         <v>1.0</v>
       </c>
       <c r="G117" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3262,13 +3262,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G118" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3288,13 +3288,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F119" t="n">
         <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3305,7 +3305,7 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
@@ -3313,17 +3313,17 @@
       <c r="D120" t="s">
         <v>33</v>
       </c>
-      <c r="E120" t="e">
-        <v>#N/A</v>
+      <c r="E120" t="s">
+        <v>44</v>
       </c>
       <c r="F120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H120" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -3339,17 +3339,17 @@
       <c r="D121" t="s">
         <v>33</v>
       </c>
-      <c r="E121" t="s">
-        <v>46</v>
+      <c r="E121" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F121" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="n">
-        <v>79.0</v>
+        <v>0.0</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
@@ -3366,13 +3366,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F122" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G122" t="n">
-        <v>24.0</v>
+        <v>79.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3392,13 +3392,13 @@
         <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F123" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="G123" t="n">
-        <v>475.0</v>
+        <v>24.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3418,13 +3418,13 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F124" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>475.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3441,16 +3441,16 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>34</v>
-      </c>
-      <c r="E125" t="e">
-        <v>#N/A</v>
+        <v>33</v>
+      </c>
+      <c r="E125" t="s">
+        <v>45</v>
       </c>
       <c r="F125" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G125" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3469,14 +3469,14 @@
       <c r="D126" t="s">
         <v>34</v>
       </c>
-      <c r="E126" t="s">
-        <v>46</v>
+      <c r="E126" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F126" t="n">
         <v>1.0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3496,13 +3496,13 @@
         <v>34</v>
       </c>
       <c r="E127" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F127" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G127" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3522,13 +3522,13 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F128" t="n">
         <v>2.0</v>
       </c>
       <c r="G128" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3545,16 +3545,16 @@
         <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G129" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3574,16 +3574,16 @@
         <v>35</v>
       </c>
       <c r="E130" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
       </c>
       <c r="G130" t="n">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="H130" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="131">
@@ -3600,16 +3600,16 @@
         <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
         <v>0.0</v>
       </c>
       <c r="G131" t="n">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="132">
@@ -3617,22 +3617,22 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
         <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3643,7 +3643,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3652,13 +3652,13 @@
         <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F133" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3678,13 +3678,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F134" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G134" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3703,14 +3703,14 @@
       <c r="D135" t="s">
         <v>36</v>
       </c>
-      <c r="E135" t="e">
-        <v>#N/A</v>
+      <c r="E135" t="s">
+        <v>47</v>
       </c>
       <c r="F135" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3729,14 +3729,14 @@
       <c r="D136" t="s">
         <v>36</v>
       </c>
-      <c r="E136" t="s">
-        <v>46</v>
+      <c r="E136" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F136" t="n">
-        <v>35.0</v>
+        <v>1.0</v>
       </c>
       <c r="G136" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3756,13 +3756,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F137" t="n">
-        <v>23.0</v>
+        <v>35.0</v>
       </c>
       <c r="G137" t="n">
-        <v>26.0</v>
+        <v>7.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3782,13 +3782,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F138" t="n">
-        <v>3.0</v>
+        <v>23.0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3808,13 +3808,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F139" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="G139" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3834,16 +3834,16 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F140" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H140" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="141">
@@ -3851,25 +3851,25 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>37</v>
-      </c>
-      <c r="E141" t="e">
-        <v>#N/A</v>
+        <v>36</v>
+      </c>
+      <c r="E141" t="s">
+        <v>45</v>
       </c>
       <c r="F141" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="142">
@@ -3885,14 +3885,14 @@
       <c r="D142" t="s">
         <v>37</v>
       </c>
-      <c r="E142" t="s">
-        <v>43</v>
+      <c r="E142" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G142" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3912,13 +3912,13 @@
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H143" t="n">
         <v>0.0</v>
@@ -3938,13 +3938,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F144" t="n">
         <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3955,7 +3955,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3963,14 +3963,14 @@
       <c r="D145" t="s">
         <v>37</v>
       </c>
-      <c r="E145" t="e">
-        <v>#N/A</v>
+      <c r="E145" t="s">
+        <v>44</v>
       </c>
       <c r="F145" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3989,14 +3989,14 @@
       <c r="D146" t="s">
         <v>37</v>
       </c>
-      <c r="E146" t="s">
-        <v>42</v>
+      <c r="E146" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F146" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G146" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4016,13 +4016,13 @@
         <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F147" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4042,13 +4042,13 @@
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G148" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4068,13 +4068,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F149" t="n">
         <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4094,7 +4094,7 @@
         <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F150" t="n">
         <v>0.0</v>
@@ -4111,7 +4111,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4120,13 +4120,13 @@
         <v>37</v>
       </c>
       <c r="E151" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F151" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4137,13 +4137,13 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E152" t="s">
         <v>46</v>
@@ -4152,7 +4152,7 @@
         <v>1.0</v>
       </c>
       <c r="G152" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4172,13 +4172,13 @@
         <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F153" t="n">
         <v>1.0</v>
       </c>
       <c r="G153" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4198,13 +4198,13 @@
         <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4224,13 +4224,13 @@
         <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F155" t="n">
         <v>0.0</v>
       </c>
       <c r="G155" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4241,7 +4241,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -4250,13 +4250,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F156" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4276,13 +4276,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F157" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4302,13 +4302,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G158" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4328,7 +4328,7 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F159" t="n">
         <v>0.0</v>
@@ -4345,22 +4345,22 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F160" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H160" t="n">
         <v>0.0</v>
@@ -4380,13 +4380,13 @@
         <v>39</v>
       </c>
       <c r="E161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F161" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G161" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4406,13 +4406,13 @@
         <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G162" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4432,13 +4432,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F163" t="n">
         <v>0.0</v>
       </c>
       <c r="G163" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4449,7 +4449,7 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -4458,13 +4458,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F164" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4483,14 +4483,14 @@
       <c r="D165" t="s">
         <v>39</v>
       </c>
-      <c r="E165" t="e">
-        <v>#N/A</v>
+      <c r="E165" t="s">
+        <v>48</v>
       </c>
       <c r="F165" t="n">
         <v>1.0</v>
       </c>
       <c r="G165" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4509,11 +4509,11 @@
       <c r="D166" t="s">
         <v>39</v>
       </c>
-      <c r="E166" t="s">
-        <v>46</v>
+      <c r="E166" t="e">
+        <v>#N/A</v>
       </c>
       <c r="F166" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G166" t="n">
         <v>1.0</v>
@@ -4536,13 +4536,13 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F167" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="G167" t="n">
-        <v>28.0</v>
+        <v>1.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4562,13 +4562,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F168" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="G168" t="n">
-        <v>5.0</v>
+        <v>28.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4588,13 +4588,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F169" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G169" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4614,13 +4614,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F170" t="n">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4631,19 +4631,19 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
       </c>
       <c r="D171" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E171" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F171" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
@@ -4666,10 +4666,10 @@
         <v>40</v>
       </c>
       <c r="E172" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F172" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G172" t="n">
         <v>0.0</v>
@@ -4692,13 +4692,13 @@
         <v>40</v>
       </c>
       <c r="E173" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F173" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G173" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H173" t="n">
         <v>0.0</v>
@@ -4718,13 +4718,13 @@
         <v>40</v>
       </c>
       <c r="E174" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F174" t="n">
         <v>1.0</v>
       </c>
       <c r="G174" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H174" t="n">
         <v>0.0</v>
@@ -4744,13 +4744,13 @@
         <v>40</v>
       </c>
       <c r="E175" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F175" t="n">
         <v>1.0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H175" t="n">
         <v>0.0</v>
@@ -4761,7 +4761,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
@@ -4770,7 +4770,7 @@
         <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F176" t="n">
         <v>1.0</v>
@@ -4796,13 +4796,13 @@
         <v>40</v>
       </c>
       <c r="E177" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F177" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G177" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -4813,19 +4813,19 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C178" t="s">
         <v>17</v>
       </c>
       <c r="D178" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E178" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F178" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G178" t="n">
         <v>1.0</v>
@@ -4848,13 +4848,13 @@
         <v>41</v>
       </c>
       <c r="E179" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F179" t="n">
         <v>1.0</v>
       </c>
       <c r="G179" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -4874,13 +4874,13 @@
         <v>41</v>
       </c>
       <c r="E180" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F180" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G180" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H180" t="n">
         <v>0.0</v>
@@ -4900,13 +4900,13 @@
         <v>41</v>
       </c>
       <c r="E181" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F181" t="n">
         <v>0.0</v>
       </c>
       <c r="G181" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="H181" t="n">
         <v>0.0</v>
@@ -4917,7 +4917,7 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C182" t="s">
         <v>17</v>
@@ -4926,13 +4926,13 @@
         <v>41</v>
       </c>
       <c r="E182" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F182" t="n">
         <v>0.0</v>
       </c>
       <c r="G182" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="H182" t="n">
         <v>0.0</v>
@@ -4952,13 +4952,13 @@
         <v>41</v>
       </c>
       <c r="E183" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F183" t="n">
         <v>0.0</v>
       </c>
       <c r="G183" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H183" t="n">
         <v>0.0</v>
@@ -4978,13 +4978,13 @@
         <v>41</v>
       </c>
       <c r="E184" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F184" t="n">
         <v>0.0</v>
       </c>
       <c r="G184" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H184" t="n">
         <v>0.0</v>
@@ -4995,7 +4995,7 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C185" t="s">
         <v>17</v>
@@ -5004,13 +5004,13 @@
         <v>41</v>
       </c>
       <c r="E185" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F185" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H185" t="n">
         <v>0.0</v>
@@ -5030,10 +5030,10 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F186" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G186" t="n">
         <v>0.0</v>
@@ -5056,13 +5056,13 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F187" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G187" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H187" t="n">
         <v>0.0</v>
@@ -5082,13 +5082,13 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F188" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H188" t="n">
         <v>0.0</v>
@@ -5108,10 +5108,10 @@
         <v>41</v>
       </c>
       <c r="E189" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F189" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G189" t="n">
         <v>0.0</v>
@@ -5134,15 +5134,41 @@
         <v>41</v>
       </c>
       <c r="E190" t="s">
+        <v>45</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>41</v>
+      </c>
+      <c r="E191" t="s">
         <v>43</v>
       </c>
-      <c r="F190" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G190" t="n">
+      <c r="F191" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G191" t="n">
         <v>4.0</v>
       </c>
-      <c r="H190" t="n">
+      <c r="H191" t="n">
         <v>0.0</v>
       </c>
     </row>
